--- a/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:02:13+00:00</t>
+    <t>2026-09-03T08:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:25:31+00:00</t>
+    <t>2026-09-03T09:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:17:44+00:00</t>
+    <t>2026-09-03T10:10:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-onko-tnm-a-symbol.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:10:01+00:00</t>
+    <t>2026-09-03T11:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
